--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_286_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_286_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3803</v>
+        <v>4.1455</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5014</v>
+        <v>4.1658</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1212</v>
+        <v>-0.0203</v>
       </c>
       <c r="G2" t="n">
         <v>5.4006</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6286</v>
+        <v>0.1366</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8883</v>
+        <v>-0.2238</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2596</v>
+        <v>0.3605</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3299</v>
+        <v>3.203</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4814</v>
+        <v>2.5561</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8485</v>
+        <v>0.6469</v>
       </c>
       <c r="G3" t="n">
         <v>0.4828</v>
@@ -688,13 +688,13 @@
         <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4734</v>
+        <v>1.3465</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5702</v>
+        <v>0.6449</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9032</v>
+        <v>0.7016</v>
       </c>
       <c r="V3" t="n">
         <v>0.6778999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3295</v>
+        <v>2.5077</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1308</v>
+        <v>2.6674</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1987</v>
+        <v>-0.1598</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2739</v>
+        <v>4.4875</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6266</v>
+        <v>1.9747</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9005</v>
+        <v>2.5128</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7423</v>
+        <v>5.213</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9005</v>
+        <v>2.2722</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6428</v>
+        <v>2.9409</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4683</v>
+        <v>-0.7255</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7261</v>
+        <v>-0.2974</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2578</v>
+        <v>-0.4281</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5711</v>
+        <v>0.5768</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6384</v>
+        <v>-0.3653</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9326</v>
+        <v>0.9421</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2836</v>
+        <v>-1.8608</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>-0.7886</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4254</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2146</v>
+        <v>2.2657</v>
       </c>
       <c r="E5" t="n">
-        <v>2.332</v>
+        <v>1.1006</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1174</v>
+        <v>1.1651</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7717000000000001</v>
+        <v>0.2739</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1523</v>
+        <v>-1.6266</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.9239</v>
+        <v>1.9005</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1104</v>
+        <v>0.7423</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4389</v>
+        <v>-0.9005</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.5493</v>
+        <v>1.6428</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6612</v>
+        <v>-0.4683</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2866</v>
+        <v>-0.7261</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3746</v>
+        <v>0.2578</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5403</v>
+        <v>2.5073</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6923</v>
+        <v>1.6083</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.152</v>
+        <v>0.899</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7501</v>
+        <v>-0.2836</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1457</v>
+        <v>2.1028</v>
       </c>
       <c r="E6" t="n">
-        <v>2.003</v>
+        <v>1.8169</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1427</v>
+        <v>0.2859</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4875</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9747</v>
+        <v>1.1523</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5128</v>
+        <v>-1.9239</v>
       </c>
       <c r="J6" t="n">
-        <v>5.213</v>
+        <v>-0.1104</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2722</v>
+        <v>1.4389</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9409</v>
+        <v>-1.5493</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7255</v>
+        <v>-0.6612</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2974</v>
+        <v>-0.2866</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4281</v>
+        <v>-0.3746</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2148</v>
+        <v>0.4285</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0297</v>
+        <v>0.1772</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2445</v>
+        <v>0.2513</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8608</v>
+        <v>1.7501</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7886</v>
+        <v>1.7501</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6014</v>
+        <v>0.8012</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7267</v>
+        <v>-0.1702</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1253</v>
+        <v>0.9714</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.952</v>
+        <v>1.1713</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0758</v>
+        <v>1.0406</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1239</v>
+        <v>0.1306</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3027</v>
+        <v>1.4644</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.507</v>
+        <v>1.17</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8097</v>
+        <v>0.2944</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2547</v>
+        <v>-0.2932</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5688</v>
+        <v>-0.1294</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6859</v>
+        <v>-0.1638</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0199</v>
+        <v>0.0422</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9085</v>
+        <v>-0.5265</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1114</v>
+        <v>0.5687</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>0.2836</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2525</v>
+        <v>0.2836</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4062</v>
+        <v>-0.2221</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5987</v>
+        <v>0.1467</v>
       </c>
       <c r="F8" t="n">
-        <v>1.005</v>
+        <v>-0.3689</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1713</v>
+        <v>0.1298</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0406</v>
+        <v>-0.6097</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1306</v>
+        <v>0.7395</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4644</v>
+        <v>0.5122</v>
       </c>
       <c r="K8" t="n">
-        <v>1.17</v>
+        <v>-0.7023</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2944</v>
+        <v>1.2146</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2932</v>
+        <v>-0.3825</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1294</v>
+        <v>0.0926</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1638</v>
+        <v>-0.4751</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3528</v>
+        <v>-0.5838</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.955</v>
+        <v>-0.3655</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6022999999999999</v>
+        <v>-0.2183</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4238</v>
+        <v>-0.4514</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1467</v>
+        <v>0.2116</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5705</v>
+        <v>-0.663</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1298</v>
+        <v>-0.952</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6097</v>
+        <v>-1.0758</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7395</v>
+        <v>0.1239</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5122</v>
+        <v>0.3027</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7023</v>
+        <v>-0.507</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2146</v>
+        <v>0.8097</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3825</v>
+        <v>-1.2547</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0926</v>
+        <v>-0.5688</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4751</v>
+        <v>-0.6859</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7855</v>
+        <v>0.9671</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3655</v>
+        <v>0.3934</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.42</v>
+        <v>0.5737</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4381</v>
+        <v>-1.9453</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4149</v>
+        <v>-1.4497</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0232</v>
+        <v>-0.4956</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3917</v>
+        <v>-2.2475</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0035</v>
+        <v>-0.066</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3881</v>
+        <v>-2.1815</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5909</v>
+        <v>-0.7501</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4671</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1239</v>
+        <v>-1.3887</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8008</v>
+        <v>-1.4974</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5365</v>
+        <v>-0.7045</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2643</v>
+        <v>-0.7929</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3453</v>
+        <v>0.5858</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4955</v>
+        <v>0.4602</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1502</v>
+        <v>0.1256</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1145</v>
+        <v>-2.229</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.35</v>
+        <v>-2.3402</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7644</v>
+        <v>0.1112</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.2475</v>
+        <v>-1.3917</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.066</v>
+        <v>-1.0035</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1815</v>
+        <v>-0.3881</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7501</v>
+        <v>-0.5909</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6385999999999999</v>
+        <v>-0.4671</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3887</v>
+        <v>-0.1239</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4974</v>
+        <v>-0.8008</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7045</v>
+        <v>-0.5365</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7929</v>
+        <v>-0.2643</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5834</v>
+        <v>0.5544</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>0.5702</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1432</v>
+        <v>-0.0158</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.8565</v>
+        <v>9.603400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>8.414299999999999</v>
+        <v>9.160900000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4423000000000001</v>
+        <v>0.4423000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>6.9336</v>
@@ -1468,13 +1468,13 @@
         <v>8.1187</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4253</v>
+        <v>6.1722</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2607</v>
+        <v>2.0076</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1645</v>
+        <v>4.164700000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1829</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8303</v>
+        <v>1.3895</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3853</v>
+        <v>2.4895</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.555</v>
+        <v>-1.1</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8692</v>
+        <v>0.0776</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.3171</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.281</v>
+        <v>0.3947</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6286</v>
+        <v>1.9471</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1443</v>
+        <v>-0.1338</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7729</v>
+        <v>2.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4978</v>
+        <v>-1.8695</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4439</v>
+        <v>-0.1833</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0539</v>
+        <v>-1.6862</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2871</v>
+        <v>0.0619</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6844</v>
+        <v>-0.8134</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6027</v>
+        <v>0.8753</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>1.3558</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3558</v>
+        <v>-1.4975</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6532</v>
+        <v>0.2862</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8998</v>
+        <v>1.7955</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2466</v>
+        <v>-1.5093</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0776</v>
+        <v>-0.8692</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3171</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3947</v>
+        <v>-0.281</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9471</v>
+        <v>0.6286</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1338</v>
+        <v>-0.1443</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0809</v>
+        <v>0.7729</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8695</v>
+        <v>-1.4978</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1833</v>
+        <v>-0.4439</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6862</v>
+        <v>-1.0539</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6743</v>
+        <v>0.7431</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4031</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7288</v>
+        <v>0.6484</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3558</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4975</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5456</v>
+        <v>-0.6904</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4036</v>
+        <v>-0.2478</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.858</v>
+        <v>-0.4426</v>
       </c>
       <c r="G16" t="n">
         <v>0.8793</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1275</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9663</v>
+        <v>0.315</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1612</v>
+        <v>0.5766</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0324</v>
+        <v>-0.7055</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4934</v>
+        <v>0.1769</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.539</v>
+        <v>-0.8825</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5611</v>
+        <v>-2.9732</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1763</v>
+        <v>-1.4741</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3848</v>
+        <v>-1.4991</v>
       </c>
       <c r="J17" t="n">
-        <v>0.104</v>
+        <v>-0.5069</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0672</v>
+        <v>-1.1659</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>0.659</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6651</v>
+        <v>-2.4663</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2435</v>
+        <v>-0.3082</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4216</v>
+        <v>-2.1581</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3992</v>
+        <v>-0.1061</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8017</v>
+        <v>0.5658</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3664</v>
+        <v>-0.7743</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8375</v>
+        <v>-0.4934</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.529</v>
+        <v>-0.2809</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7866</v>
+        <v>-0.5611</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8729</v>
+        <v>-0.1763</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6595</v>
+        <v>-0.3848</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8394</v>
+        <v>0.104</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6554</v>
+        <v>0.0672</v>
       </c>
       <c r="L18" t="n">
-        <v>0.184</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.626</v>
+        <v>-0.6651</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2175</v>
+        <v>-0.2435</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8435</v>
+        <v>-0.4216</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0411</v>
+        <v>-1.1411</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8883</v>
+        <v>-0.5975</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1529</v>
+        <v>-0.5436</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4001</v>
+        <v>-0.7792</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8358</v>
+        <v>-0.2551</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5644</v>
+        <v>-0.5241</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1576</v>
+        <v>-2.3935</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8704</v>
+        <v>-0.9113</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7127</v>
+        <v>-1.4822</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6974</v>
+        <v>-0.2135</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0923</v>
+        <v>-0.6785</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3949</v>
+        <v>0.465</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-2.18</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.222</v>
+        <v>-0.2327</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3178</v>
+        <v>-1.9473</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8619</v>
+        <v>-0.0815</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3734</v>
+        <v>-0.5777</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4885</v>
+        <v>0.4962</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4748</v>
+        <v>-1.02</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.491</v>
+        <v>0.7788</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9838</v>
+        <v>-1.7987</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3935</v>
+        <v>0.498</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9113</v>
+        <v>2.4789</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4822</v>
+        <v>-1.9809</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2135</v>
+        <v>2.1742</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6785</v>
+        <v>2.8905</v>
       </c>
       <c r="L20" t="n">
-        <v>0.465</v>
+        <v>-0.7163</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.18</v>
+        <v>-1.6762</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2327</v>
+        <v>-0.4116</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9473</v>
+        <v>-1.2647</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7771</v>
+        <v>-0.9818</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8136</v>
+        <v>-0.2357</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0365</v>
+        <v>-0.7461</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5361</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6098</v>
+        <v>-1.2256</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4128</v>
+        <v>-0.7195</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.197</v>
+        <v>-0.5061</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9732</v>
+        <v>-0.7866</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4741</v>
+        <v>0.8729</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4991</v>
+        <v>-1.6595</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5069</v>
+        <v>0.8394</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1659</v>
+        <v>0.6554</v>
       </c>
       <c r="L21" t="n">
-        <v>0.659</v>
+        <v>0.184</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4663</v>
+        <v>-1.626</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3082</v>
+        <v>0.2175</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1581</v>
+        <v>-1.8435</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0104</v>
+        <v>-0.9003</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2617</v>
+        <v>-0.7703</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2513</v>
+        <v>-0.13</v>
       </c>
       <c r="V21" t="n">
-        <v>1.214</v>
+        <v>-0.9304</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3558</v>
+        <v>-0.7886</v>
       </c>
       <c r="X21" t="n">
         <v>-0.1418</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6991</v>
+        <v>-1.3265</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4249</v>
+        <v>-0.7178</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.124</v>
+        <v>-0.6087</v>
       </c>
       <c r="G22" t="n">
-        <v>0.498</v>
+        <v>0.1576</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4789</v>
+        <v>0.8704</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9809</v>
+        <v>-0.7127</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1742</v>
+        <v>0.6974</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8905</v>
+        <v>1.0923</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7163</v>
+        <v>-0.3949</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6762</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4116</v>
+        <v>-0.222</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2647</v>
+        <v>-0.3178</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.661</v>
+        <v>-0.7883</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>-0.2555</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0714</v>
+        <v>-0.5329</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3029</v>
+        <v>-1.6516</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4853</v>
+        <v>-3.2494</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1824</v>
+        <v>1.5978</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9627</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.415</v>
+        <v>-0.7637</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8883</v>
+        <v>-0.6524</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.1114</v>
       </c>
       <c r="V23" t="n">
         <v>1.4665</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.856400000000001</v>
+        <v>-6.497400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4422000000000001</v>
+        <v>-0.4422999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.414400000000001</v>
+        <v>-6.055099999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-6.933799999999999</v>
@@ -2302,7 +2302,7 @@
         <v>7.6314</v>
       </c>
       <c r="K24" t="n">
-        <v>4.169500000000001</v>
+        <v>4.169499999999999</v>
       </c>
       <c r="L24" t="n">
         <v>3.4619</v>
@@ -2317,7 +2317,7 @@
         <v>-12.6469</v>
       </c>
       <c r="P24" t="n">
-        <v>2.319599999999999</v>
+        <v>2.3196</v>
       </c>
       <c r="Q24" t="n">
         <v>-8.118399999999999</v>
@@ -2326,13 +2326,13 @@
         <v>10.438</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.425400000000001</v>
+        <v>-3.0662</v>
       </c>
       <c r="T24" t="n">
         <v>-4.1647</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2607</v>
+        <v>1.0983</v>
       </c>
       <c r="V24" t="n">
         <v>1.1829</v>
